--- a/artfynd/A 8978-2024 artfynd.xlsx
+++ b/artfynd/A 8978-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120756564</v>
+        <v>120756594</v>
       </c>
       <c r="B2" t="n">
-        <v>97025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>NV om Strängsered, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419763</v>
+        <v>419777</v>
       </c>
       <c r="R2" t="n">
-        <v>6405705</v>
+        <v>6405884</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I liten damm vid dike.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +779,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Svensson, Jonas Örnborg</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -784,12 +798,7 @@
         <v>120756606</v>
       </c>
       <c r="B3" t="n">
-        <v>58205</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,12 +909,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -916,15 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120756613</v>
+        <v>120756609</v>
       </c>
       <c r="B4" t="n">
-        <v>58205</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,17 +953,31 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>NV om Strängsered, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>419706</v>
+        <v>419775</v>
       </c>
       <c r="R4" t="n">
-        <v>6405711</v>
+        <v>6405884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,9 +1007,24 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I dammliknande dike.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,15 +1039,217 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Svensson, Jonas Örnborg</t>
+          <t>Andreas Ekedahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Strängsered 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120756613</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NV om Strängsered, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>419706</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6405711</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gullered</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl, Jonas Örnborg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering vid Strängsered 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120756564</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NV om Strängsered, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>419763</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6405705</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gullered</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl, Jonas Örnborg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>

--- a/artfynd/A 8978-2024 artfynd.xlsx
+++ b/artfynd/A 8978-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756594</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756606</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,6 +1067,11 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756609</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756613</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1254,8 +1279,20 @@
           <t>Naturvärdesinventering vid Strängsered 2024</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120756564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>